--- a/server/lookup_tables/codigos modelos nissan.xlsx
+++ b/server/lookup_tables/codigos modelos nissan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen Virga\Desktop\gabi actis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lisandro Santori\Documents\Neostar\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Código</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>X-TRAIL 2.5 EXCLUSIVE CVT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                                                                                                                                                                        *</t>
   </si>
   <si>
     <t xml:space="preserve">VERSA 1.6 SENSE MT </t>
@@ -264,7 +261,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -272,133 +269,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.44140625" customWidth="1"/>
@@ -695,260 +582,260 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>38</v>
+      <c r="B8" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="8" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8" t="s">
+    <row r="15" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>54</v>
+      <c r="B22" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>55</v>
+      <c r="B23" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>56</v>
+      <c r="B24" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>57</v>
+      <c r="B25" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>58</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>59</v>
+      <c r="B27" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>60</v>
+      <c r="B28" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -974,18 +861,6 @@
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B40" s="2"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
